--- a/docs/TBP Template v1 (version 1).xlsx
+++ b/docs/TBP Template v1 (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jimit\Desktop\Course 2\Sem 2\Case studies\AI_PREDICTOR\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C8C34F-609F-4A94-BA2E-E18D18CE55F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F397C9-CC2F-48B6-BD09-4714ED0E3707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WHMcNumber" sheetId="13" state="hidden" r:id="rId1"/>
@@ -648,13 +648,13 @@
     <t>Jay and vishal</t>
   </si>
   <si>
-    <t>Reduce the number of derivative traders experiencing losses from 90% to 70% within 3 months</t>
-  </si>
-  <si>
     <t>Deliver personalized trading education modules</t>
   </si>
   <si>
     <t>Achieve a 50% increase in stop-loss compliance</t>
+  </si>
+  <si>
+    <t>Reduce number of options traders with lack of knowledge experiencing losses within 3 months</t>
   </si>
 </sst>
 </file>
@@ -992,7 +992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1211,6 +1211,15 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1277,6 +1286,51 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1285,51 +1339,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4070,22 +4079,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>196392</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>23568</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>2238375</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>124371</xdr:rowOff>
+      <xdr:colOff>2246722</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>141403</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB19073-E2A5-49A0-D626-D9A4B7E2558B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1C9216F-15A3-4860-D007-551051D903B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4101,8 +4110,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6200775" y="1485900"/>
-          <a:ext cx="5476875" cy="3915321"/>
+          <a:off x="6284536" y="1437589"/>
+          <a:ext cx="5388990" cy="4846948"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4114,22 +4123,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>16933</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>8467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>2379135</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EE283E0-E2C4-7416-C8B9-60F5C9D905C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E2D7674-D1DE-8EFA-B43A-D734B1857228}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4145,8 +4154,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6162675" y="6657975"/>
-          <a:ext cx="5734050" cy="1828800"/>
+          <a:off x="6121400" y="6731000"/>
+          <a:ext cx="5698068" cy="1744133"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4158,22 +4167,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>42332</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>118532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2302932</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>194732</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D362B415-0A8F-AD95-9C26-82CC5F8A4F35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB49E94E-4262-445F-1ACA-31F9688BA9D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4189,8 +4198,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="219075" y="1476375"/>
-          <a:ext cx="5781675" cy="2295525"/>
+          <a:off x="228599" y="1566332"/>
+          <a:ext cx="5613400" cy="2218267"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4201,23 +4210,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>16933</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>203201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2409826</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>29084</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>16933</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13">
+        <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D52AE13-CC32-B238-7C81-1B5E0634A3C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DC5F40E-2255-1372-191B-A801483C80A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4233,8 +4242,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="257176" y="4171950"/>
-          <a:ext cx="5695950" cy="3648584"/>
+          <a:off x="6121400" y="6697134"/>
+          <a:ext cx="5782733" cy="1854200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15507</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135468</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>3795</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>143934</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F221243-49BA-3A91-69D3-DECF9ACBA6AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="201774" y="4343401"/>
+          <a:ext cx="5787954" cy="3208866"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4691,10 +4744,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="74"/>
+      <c r="B1" s="77"/>
     </row>
     <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
@@ -4886,10 +4939,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="77"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
@@ -4900,13 +4953,13 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="78"/>
+      <c r="B3" s="81"/>
     </row>
     <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="42" t="s">
@@ -4914,22 +4967,22 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="79"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="43" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="44" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="81"/>
+      <c r="B7" s="84"/>
     </row>
     <row r="8" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
@@ -4940,10 +4993,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="79"/>
     </row>
     <row r="10" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
@@ -4954,10 +5007,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="79"/>
     </row>
     <row r="12" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
@@ -4968,13 +5021,13 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="76"/>
+      <c r="B13" s="79"/>
     </row>
     <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="85" t="s">
         <v>53</v>
       </c>
       <c r="B14" s="42" t="s">
@@ -4982,19 +5035,19 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="83"/>
+      <c r="A15" s="86"/>
       <c r="B15" s="44" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="76"/>
+      <c r="B16" s="79"/>
     </row>
     <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="85" t="s">
         <v>56</v>
       </c>
       <c r="B17" s="42" t="s">
@@ -5002,16 +5055,16 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="83"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="44" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="76"/>
+      <c r="B19" s="79"/>
     </row>
     <row r="20" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
@@ -5022,10 +5075,10 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="76"/>
+      <c r="B21" s="79"/>
     </row>
     <row r="22" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
@@ -5090,33 +5143,33 @@
     <row r="1" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="115"/>
+      <c r="C2" s="118"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="114" t="s">
+      <c r="E2" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="115"/>
-      <c r="H2" s="114" t="s">
+      <c r="F2" s="118"/>
+      <c r="H2" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="115"/>
-      <c r="K2" s="123" t="s">
+      <c r="I2" s="118"/>
+      <c r="K2" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="124"/>
+      <c r="L2" s="127"/>
       <c r="M2" s="7"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="122"/>
+      <c r="C3" s="125"/>
       <c r="D3" s="5"/>
       <c r="E3" s="8" t="s">
         <v>0</v>
@@ -5130,10 +5183,10 @@
       <c r="I3" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="126"/>
-      <c r="L3" s="127"/>
-      <c r="N3" s="125"/>
-      <c r="O3" s="125"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="130"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -5153,15 +5206,15 @@
         <v>81</v>
       </c>
       <c r="L4" s="7"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="125"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="114" t="s">
+      <c r="B5" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="115"/>
+      <c r="C5" s="118"/>
       <c r="D5" s="5"/>
       <c r="E5" s="2" t="s">
         <v>2</v>
@@ -5175,17 +5228,17 @@
       <c r="I5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="128" t="s">
+      <c r="K5" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="128"/>
-      <c r="N5" s="125"/>
-      <c r="O5" s="125"/>
+      <c r="L5" s="131"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="121"/>
-      <c r="C6" s="122"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="125"/>
       <c r="D6" s="5"/>
       <c r="E6" s="10" t="s">
         <v>3</v>
@@ -5197,10 +5250,10 @@
         <v>3</v>
       </c>
       <c r="I6" s="11"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
-      <c r="N6" s="125"/>
-      <c r="O6" s="125"/>
+      <c r="K6" s="132"/>
+      <c r="L6" s="132"/>
+      <c r="N6" s="128"/>
+      <c r="O6" s="128"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
@@ -5215,13 +5268,13 @@
     </row>
     <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="118"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="121"/>
       <c r="G8" s="13"/>
       <c r="H8" s="111" t="s">
         <v>41</v>
@@ -5231,24 +5284,24 @@
       <c r="K8" s="112"/>
       <c r="L8" s="113"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="84" t="s">
+      <c r="N8" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="85"/>
+      <c r="O8" s="88"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="22"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="120"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="123"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="88"/>
-      <c r="L9" s="89"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="92"/>
       <c r="M9" s="14"/>
       <c r="N9" s="50"/>
       <c r="O9" s="46"/>
@@ -5261,11 +5314,11 @@
       <c r="E10" s="100"/>
       <c r="F10" s="101"/>
       <c r="G10" s="13"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="92"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="95"/>
       <c r="N10" s="3"/>
       <c r="O10" s="47"/>
     </row>
@@ -5277,11 +5330,11 @@
       <c r="E11" s="100"/>
       <c r="F11" s="101"/>
       <c r="G11" s="13"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="91"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="92"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="95"/>
       <c r="N11" s="3"/>
       <c r="O11" s="47"/>
     </row>
@@ -5293,11 +5346,11 @@
       <c r="E12" s="19"/>
       <c r="F12" s="20"/>
       <c r="G12" s="13"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="92"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="95"/>
       <c r="N12" s="3"/>
       <c r="O12" s="47"/>
     </row>
@@ -5309,11 +5362,11 @@
       <c r="E13" s="69"/>
       <c r="F13" s="70"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="92"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="95"/>
       <c r="N13" s="3"/>
       <c r="O13" s="47"/>
     </row>
@@ -5325,11 +5378,11 @@
       <c r="E14" s="69"/>
       <c r="F14" s="70"/>
       <c r="G14" s="13"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="92"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="94"/>
+      <c r="L14" s="95"/>
       <c r="N14" s="3"/>
       <c r="O14" s="47"/>
     </row>
@@ -5341,11 +5394,11 @@
       <c r="E15" s="69"/>
       <c r="F15" s="70"/>
       <c r="G15" s="13"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="92"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="94"/>
+      <c r="L15" s="95"/>
       <c r="N15" s="3"/>
       <c r="O15" s="47"/>
     </row>
@@ -5357,11 +5410,11 @@
       <c r="E16" s="69"/>
       <c r="F16" s="70"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="92"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="94"/>
+      <c r="L16" s="95"/>
       <c r="N16" s="3"/>
       <c r="O16" s="47"/>
     </row>
@@ -5373,11 +5426,11 @@
       <c r="E17" s="69"/>
       <c r="F17" s="70"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="92"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="95"/>
       <c r="N17" s="3"/>
       <c r="O17" s="47"/>
     </row>
@@ -5389,11 +5442,11 @@
       <c r="E18" s="69"/>
       <c r="F18" s="70"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="92"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="95"/>
       <c r="N18" s="3"/>
       <c r="O18" s="47"/>
     </row>
@@ -5405,11 +5458,11 @@
       <c r="E19" s="69"/>
       <c r="F19" s="70"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="92"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="95"/>
       <c r="N19" s="3"/>
       <c r="O19" s="47"/>
     </row>
@@ -5421,11 +5474,11 @@
       <c r="E20" s="69"/>
       <c r="F20" s="70"/>
       <c r="G20" s="13"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="92"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="94"/>
+      <c r="L20" s="95"/>
       <c r="N20" s="3"/>
       <c r="O20" s="47"/>
     </row>
@@ -5437,201 +5490,201 @@
       <c r="E21" s="71"/>
       <c r="F21" s="72"/>
       <c r="G21" s="13"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="91"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="92"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="95"/>
       <c r="N21" s="3"/>
       <c r="O21" s="47"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="85"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="88"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="92"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="95"/>
       <c r="N22" s="3"/>
       <c r="O22" s="47"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="92"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="95"/>
       <c r="G23" s="13"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="92"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
+      <c r="L23" s="95"/>
       <c r="N23" s="3"/>
       <c r="O23" s="47"/>
     </row>
     <row r="24" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="90"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="92"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="95"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="92"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="95"/>
       <c r="N24" s="3"/>
       <c r="O24" s="47"/>
     </row>
     <row r="25" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="92"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="95"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="92"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="95"/>
       <c r="N25" s="65"/>
       <c r="O25" s="48"/>
     </row>
     <row r="26" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="92"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="94"/>
+      <c r="D26" s="94"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="95"/>
       <c r="G26" s="13"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="91"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="92"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="94"/>
+      <c r="L26" s="95"/>
       <c r="N26" s="65"/>
       <c r="O26" s="48"/>
     </row>
     <row r="27" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="92"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="95"/>
       <c r="G27" s="13"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="92"/>
-      <c r="N27" s="84" t="s">
+      <c r="H27" s="93"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="95"/>
+      <c r="N27" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="O27" s="85"/>
+      <c r="O27" s="88"/>
     </row>
     <row r="28" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="92"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="95"/>
       <c r="G28" s="13"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="92"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="94"/>
+      <c r="K28" s="94"/>
+      <c r="L28" s="95"/>
       <c r="N28" s="49"/>
       <c r="O28" s="45"/>
     </row>
     <row r="29" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="91"/>
-      <c r="F29" s="92"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="95"/>
       <c r="G29" s="13"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="92"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="95"/>
       <c r="N29" s="3"/>
       <c r="O29" s="15"/>
     </row>
     <row r="30" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="92"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="95"/>
       <c r="G30" s="13"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="91"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="92"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="95"/>
       <c r="N30" s="3"/>
       <c r="O30" s="15"/>
     </row>
     <row r="31" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="92"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="95"/>
       <c r="G31" s="13"/>
-      <c r="H31" s="90"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="92"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="94"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="95"/>
       <c r="N31" s="3"/>
       <c r="O31" s="15"/>
     </row>
     <row r="32" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="92"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="95"/>
       <c r="G32" s="13"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="94"/>
-      <c r="L32" s="95"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="98"/>
       <c r="N32" s="110"/>
       <c r="O32" s="109"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="92"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="95"/>
       <c r="G33" s="13"/>
       <c r="H33" s="102" t="s">
         <v>68</v>
@@ -5645,11 +5698,11 @@
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="90"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="95"/>
       <c r="G34" s="13"/>
       <c r="H34" s="50"/>
       <c r="I34" s="51"/>
@@ -5661,11 +5714,11 @@
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
-      <c r="B35" s="90"/>
-      <c r="C35" s="91"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="92"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="95"/>
       <c r="G35" s="13"/>
       <c r="H35" s="53"/>
       <c r="I35" s="54"/>
@@ -5677,11 +5730,11 @@
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="91"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="92"/>
+      <c r="B36" s="93"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="95"/>
       <c r="G36" s="13"/>
       <c r="H36" s="53"/>
       <c r="I36" s="58"/>
@@ -5693,11 +5746,11 @@
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
-      <c r="B37" s="90"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="92"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="95"/>
       <c r="G37" s="13"/>
       <c r="H37" s="60"/>
       <c r="I37" s="55"/>
@@ -5709,11 +5762,11 @@
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
-      <c r="B38" s="90"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="92"/>
+      <c r="B38" s="93"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
+      <c r="F38" s="95"/>
       <c r="G38" s="13"/>
       <c r="H38" s="53"/>
       <c r="I38" s="58"/>
@@ -5725,11 +5778,11 @@
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
-      <c r="B39" s="90"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="92"/>
+      <c r="B39" s="93"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
+      <c r="F39" s="95"/>
       <c r="G39" s="13"/>
       <c r="H39" s="60"/>
       <c r="I39" s="55"/>
@@ -5741,11 +5794,11 @@
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="90"/>
-      <c r="C40" s="91"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="92"/>
+      <c r="B40" s="93"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
+      <c r="F40" s="95"/>
       <c r="G40" s="13"/>
       <c r="H40" s="61"/>
       <c r="I40" s="55"/>
@@ -5757,11 +5810,11 @@
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="92"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="95"/>
       <c r="G41" s="13"/>
       <c r="H41" s="61"/>
       <c r="I41" s="55"/>
@@ -5773,11 +5826,11 @@
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
-      <c r="B42" s="90"/>
-      <c r="C42" s="91"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="92"/>
+      <c r="B42" s="93"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="95"/>
       <c r="G42" s="13"/>
       <c r="H42" s="111" t="s">
         <v>71</v>
@@ -5791,11 +5844,11 @@
     </row>
     <row r="43" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
-      <c r="B43" s="93"/>
-      <c r="C43" s="94"/>
-      <c r="D43" s="94"/>
-      <c r="E43" s="94"/>
-      <c r="F43" s="95"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="97"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="98"/>
       <c r="G43" s="13"/>
       <c r="H43" s="50"/>
       <c r="I43" s="64"/>
@@ -5806,13 +5859,13 @@
       <c r="O43" s="109"/>
     </row>
     <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="84" t="s">
+      <c r="B44" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="86"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="85"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="88"/>
       <c r="G44" s="13"/>
       <c r="H44" s="3"/>
       <c r="I44" s="6"/>
@@ -5826,12 +5879,12 @@
       <c r="B45" s="17">
         <v>1</v>
       </c>
-      <c r="C45" s="96" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="97"/>
-      <c r="E45" s="97"/>
-      <c r="F45" s="98"/>
+      <c r="C45" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="75"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="76"/>
       <c r="G45" s="13"/>
       <c r="H45" s="3"/>
       <c r="I45" s="6"/>
@@ -5845,12 +5898,12 @@
       <c r="B46" s="17">
         <v>2</v>
       </c>
-      <c r="C46" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="97"/>
-      <c r="E46" s="97"/>
-      <c r="F46" s="98"/>
+      <c r="C46" s="114" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="115"/>
+      <c r="E46" s="115"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="13"/>
       <c r="H46" s="3"/>
       <c r="I46" s="6"/>
@@ -5865,7 +5918,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="105" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D47" s="105"/>
       <c r="E47" s="105"/>
@@ -5960,7 +6013,7 @@
     <row r="110" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="111" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="30">
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="H8:L8"/>
@@ -5989,7 +6042,6 @@
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="H9:L32"/>
-    <mergeCell ref="C45:F45"/>
     <mergeCell ref="B10:F11"/>
     <mergeCell ref="H33:L33"/>
   </mergeCells>
